--- a/app/reports/NA_research.xlsx
+++ b/app/reports/NA_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-07-31 17:38 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-01 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04736999988555908</v>
+        <v>0.04744999885559082</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>23214088.39779006</v>
+        <v>23214089.38547486</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="38">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>42017500</v>
+        <v>41553220</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>-3.67</v>
+        <v>-3.66</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>8.640000000000001</v>
+        <v>8.609999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1532,16 +1532,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>270828704</v>
+        <v>268206096</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>86.05555</v>
+        <v>85.22221999999999</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>25.467</v>
+        <v>26.44</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>2.648</v>
+        <v>2.749</v>
       </c>
     </row>
     <row r="7">
@@ -1556,14 +1556,14 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>201132224</v>
+        <v>199777136</v>
       </c>
       <c r="D7" s="33" t="n"/>
       <c r="E7" s="33" t="n">
-        <v>-7.475</v>
+        <v>-7.603</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>2184.444</v>
+        <v>2222.085</v>
       </c>
     </row>
     <row r="8">
@@ -1578,14 +1578,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>174194160</v>
+        <v>169191200</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>-6.104</v>
+        <v>-6.031</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>48.498</v>
+        <v>47.917</v>
       </c>
     </row>
     <row r="9">
@@ -1600,14 +1600,14 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>64096588</v>
+        <v>63376404</v>
       </c>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="33" t="n">
-        <v>3.366</v>
+        <v>3.448</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>-2.496</v>
+        <v>-2.557</v>
       </c>
     </row>
     <row r="10">
@@ -1622,16 +1622,16 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>44203736</v>
+        <v>44531984</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>1.9056605</v>
+        <v>1.9198115</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>-407.757</v>
+        <v>-407.717</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>-5.357</v>
+        <v>-5.356</v>
       </c>
     </row>
     <row r="11">
@@ -1646,14 +1646,14 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>25609772</v>
+        <v>25533778</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
-        <v>-0.958</v>
+        <v>-0.966</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>3.74</v>
+        <v>3.769</v>
       </c>
     </row>
     <row r="12">
@@ -1668,14 +1668,14 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>118657864</v>
+        <v>119022968</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n">
-        <v>-3.192</v>
+        <v>-2.896</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>0.364</v>
+        <v>0.417</v>
       </c>
     </row>
     <row r="13">
@@ -1690,14 +1690,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>232174752</v>
+        <v>228927360</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>-20.705</v>
+        <v>-21.524</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>2.585</v>
+        <v>2.687</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/NA_research.xlsx
+++ b/app/reports/NA_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-01 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-02 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>

--- a/app/reports/NA_research.xlsx
+++ b/app/reports/NA_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-02 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-03 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1.79</v>
+        <v>1.865</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04744999885559082</v>
+        <v>0.04690000057220459</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>23214089.38547486</v>
+        <v>23214091.15281501</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>1.79</v>
+        <v>1.865</v>
       </c>
     </row>
     <row r="38">
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>41553220</v>
+        <v>43294280</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>1.77</v>
+        <v>1.85</v>
       </c>
       <c r="E5" s="31" t="n">
         <v>-3.66</v>
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>268206096</v>
+        <v>272926784</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>85.22221999999999</v>
+        <v>86.72221</v>
       </c>
       <c r="E6" s="33" t="n">
         <v>26.44</v>
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>199777136</v>
+        <v>203261632</v>
       </c>
       <c r="D7" s="33" t="n"/>
       <c r="E7" s="33" t="n">
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>169191200</v>
+        <v>183745280</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>63376404</v>
+        <v>65056836</v>
       </c>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="33" t="n">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>44531984</v>
+        <v>44825212</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>1.9198115</v>
+        <v>1.9324529</v>
       </c>
       <c r="E10" s="33" t="n">
         <v>-407.717</v>
@@ -1646,7 +1646,7 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>25533778</v>
+        <v>25837754</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>119022968</v>
+        <v>124134384</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n">
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>228927360</v>
+        <v>235163504</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">

--- a/app/reports/NA_research.xlsx
+++ b/app/reports/NA_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-03 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-04 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1.865</v>
+        <v>1.91</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04690000057220459</v>
+        <v>0.0463100004196167</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>23214091.15281501</v>
+        <v>23214090.05235602</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>1.865</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="38">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>43294280</v>
+        <v>44338912</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>-3.66</v>
+        <v>-3.68</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>8.609999999999999</v>
+        <v>8.66</v>
       </c>
     </row>
     <row r="6">
@@ -1532,16 +1532,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>272926784</v>
+        <v>300201984</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>86.72221</v>
+        <v>95.388885</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>26.44</v>
+        <v>27.077</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>2.749</v>
+        <v>2.815</v>
       </c>
     </row>
     <row r="7">
@@ -1556,14 +1556,14 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>203261632</v>
+        <v>221458368</v>
       </c>
       <c r="D7" s="33" t="n"/>
       <c r="E7" s="33" t="n">
-        <v>-7.603</v>
+        <v>-7.843</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>2222.085</v>
+        <v>2291.99</v>
       </c>
     </row>
     <row r="8">
@@ -1578,14 +1578,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>183745280</v>
+        <v>207850480</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>-6.031</v>
+        <v>-6.421</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>47.917</v>
+        <v>51.016</v>
       </c>
     </row>
     <row r="9">
@@ -1604,10 +1604,10 @@
       </c>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="33" t="n">
-        <v>3.448</v>
+        <v>3.366</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>-2.557</v>
+        <v>-2.496</v>
       </c>
     </row>
     <row r="10">
@@ -1622,13 +1622,13 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>44825212</v>
+        <v>44313156</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>1.9324529</v>
+        <v>1.8925234</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>-407.717</v>
+        <v>-407.737</v>
       </c>
       <c r="F10" s="33" t="n">
         <v>-5.356</v>
@@ -1646,14 +1646,14 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>25837754</v>
+        <v>27129640</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
-        <v>-0.966</v>
+        <v>-0.98</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>3.769</v>
+        <v>3.826</v>
       </c>
     </row>
     <row r="12">
@@ -1668,14 +1668,14 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>124134384</v>
+        <v>134357216</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n">
-        <v>-2.896</v>
+        <v>-3.195</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>0.417</v>
+        <v>0.461</v>
       </c>
     </row>
     <row r="13">
@@ -1690,14 +1690,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>235163504</v>
+        <v>262366944</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>-21.524</v>
+        <v>-22.362</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>2.687</v>
+        <v>2.791</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/NA_research.xlsx
+++ b/app/reports/NA_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-04 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-05 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.0463100004196167</v>
+        <v>0.04620999813079834</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>23214090.05235602</v>
+        <v>23214090.32258064</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="38">
@@ -1508,10 +1508,10 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>44338912</v>
+        <v>43178208</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="E5" s="31" t="n">
         <v>-3.68</v>
@@ -1532,10 +1532,10 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>300201984</v>
+        <v>292159296</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>95.388885</v>
+        <v>92.83333</v>
       </c>
       <c r="E6" s="33" t="n">
         <v>27.077</v>
@@ -1556,7 +1556,7 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>221458368</v>
+        <v>205584608</v>
       </c>
       <c r="D7" s="33" t="n"/>
       <c r="E7" s="33" t="n">
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>207850480</v>
+        <v>207386576</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
@@ -1600,7 +1600,7 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>65056836</v>
+        <v>62776244</v>
       </c>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="33" t="n">
@@ -1625,10 +1625,10 @@
         <v>44313156</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>1.8925234</v>
+        <v>1.9103775</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>-407.737</v>
+        <v>-407.707</v>
       </c>
       <c r="F10" s="33" t="n">
         <v>-5.356</v>
@@ -1646,7 +1646,7 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>27129640</v>
+        <v>26901660</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
@@ -1668,7 +1668,7 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>134357216</v>
+        <v>133627016</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n">
@@ -1690,14 +1690,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>262366944</v>
+        <v>253986928</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>-22.362</v>
+        <v>-25.602</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>2.791</v>
+        <v>3.196</v>
       </c>
     </row>
     <row r="15">

--- a/app/reports/NA_research.xlsx
+++ b/app/reports/NA_research.xlsx
@@ -620,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-08-05 17:35 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
+          <t>Generated 2026-08-06 17:36 · Source: FMP · Methodology: financial-analysis plugin (Anthropic FSI), adapted for free-tier data</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.04620999813079834</v>
+        <v>0.04668000221252441</v>
       </c>
     </row>
     <row r="6">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B35" s="20" t="n">
-        <v>23214090.32258064</v>
+        <v>23214090.81081081</v>
       </c>
     </row>
     <row r="36">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="B37" s="22" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="38">
@@ -1508,16 +1508,16 @@
         </is>
       </c>
       <c r="C5" s="30" t="n">
-        <v>43178208</v>
+        <v>42946068</v>
       </c>
       <c r="D5" s="31" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="E5" s="31" t="n">
-        <v>-3.68</v>
+        <v>-3.71</v>
       </c>
       <c r="F5" s="31" t="n">
-        <v>8.66</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="6">
@@ -1532,16 +1532,16 @@
         </is>
       </c>
       <c r="C6" s="32" t="n">
-        <v>292159296</v>
+        <v>272314848</v>
       </c>
       <c r="D6" s="33" t="n">
-        <v>92.83333</v>
+        <v>86.52777</v>
       </c>
       <c r="E6" s="33" t="n">
-        <v>27.077</v>
+        <v>27.625</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>2.815</v>
+        <v>2.873</v>
       </c>
     </row>
     <row r="7">
@@ -1556,14 +1556,14 @@
         </is>
       </c>
       <c r="C7" s="32" t="n">
-        <v>205584608</v>
+        <v>208294768</v>
       </c>
       <c r="D7" s="33" t="n"/>
       <c r="E7" s="33" t="n">
-        <v>-7.843</v>
+        <v>-7.406</v>
       </c>
       <c r="F7" s="33" t="n">
-        <v>2291.99</v>
+        <v>727.3819999999999</v>
       </c>
     </row>
     <row r="8">
@@ -1578,14 +1578,14 @@
         </is>
       </c>
       <c r="C8" s="32" t="n">
-        <v>207386576</v>
+        <v>220717904</v>
       </c>
       <c r="D8" s="33" t="n"/>
       <c r="E8" s="33" t="n">
-        <v>-6.421</v>
+        <v>-7.03</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>51.016</v>
+        <v>55.857</v>
       </c>
     </row>
     <row r="9">
@@ -1600,14 +1600,14 @@
         </is>
       </c>
       <c r="C9" s="32" t="n">
-        <v>62776244</v>
+        <v>63136340</v>
       </c>
       <c r="D9" s="33" t="n"/>
       <c r="E9" s="33" t="n">
-        <v>3.366</v>
+        <v>3.503</v>
       </c>
       <c r="F9" s="33" t="n">
-        <v>-2.496</v>
+        <v>-2.598</v>
       </c>
     </row>
     <row r="10">
@@ -1622,16 +1622,16 @@
         </is>
       </c>
       <c r="C10" s="32" t="n">
-        <v>44313156</v>
+        <v>44367856</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>1.9103775</v>
+        <v>1.9127358</v>
       </c>
       <c r="E10" s="33" t="n">
-        <v>-407.707</v>
+        <v>-407.796</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>-5.356</v>
+        <v>-5.357</v>
       </c>
     </row>
     <row r="11">
@@ -1646,14 +1646,14 @@
         </is>
       </c>
       <c r="C11" s="32" t="n">
-        <v>26901660</v>
+        <v>26369706</v>
       </c>
       <c r="D11" s="33" t="n"/>
       <c r="E11" s="33" t="n">
-        <v>-0.98</v>
+        <v>-1.005</v>
       </c>
       <c r="F11" s="33" t="n">
-        <v>3.826</v>
+        <v>3.921</v>
       </c>
     </row>
     <row r="12">
@@ -1668,14 +1668,14 @@
         </is>
       </c>
       <c r="C12" s="32" t="n">
-        <v>133627016</v>
+        <v>144580048</v>
       </c>
       <c r="D12" s="33" t="n"/>
       <c r="E12" s="33" t="n">
-        <v>-3.195</v>
+        <v>-3.481</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>0.461</v>
+        <v>0.502</v>
       </c>
     </row>
     <row r="13">
@@ -1690,14 +1690,14 @@
         </is>
       </c>
       <c r="C13" s="32" t="n">
-        <v>253986928</v>
+        <v>249733696</v>
       </c>
       <c r="D13" s="33" t="n"/>
       <c r="E13" s="33" t="n">
-        <v>-25.602</v>
+        <v>-24.128</v>
       </c>
       <c r="F13" s="33" t="n">
-        <v>3.196</v>
+        <v>3.012</v>
       </c>
     </row>
     <row r="15">
